--- a/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/AssetDeclarationCodeMaintenance001.xlsx
+++ b/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/AssetDeclarationCodeMaintenance001.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>资产代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -46,19 +46,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>回售</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>标准券出入库</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>可转债信用申购</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可转债转股</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -462,7 +450,7 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E1" t="s">
         <v>1</v>
@@ -486,7 +474,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Sheet2!$A$2:$A$8</xm:f>
+            <xm:f>Sheet2!$A$2:$A$5</xm:f>
           </x14:formula1>
           <xm:sqref>D2:D1048576</xm:sqref>
         </x14:dataValidation>
@@ -498,7 +486,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.26953125" bestFit="1" customWidth="1"/>
@@ -506,7 +494,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -537,21 +525,6 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/AssetDeclarationCodeMaintenance001.xlsx
+++ b/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/AssetDeclarationCodeMaintenance001.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>资产代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -63,6 +63,26 @@
   </si>
   <si>
     <t>业务类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基金分红设置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资产类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>债券</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基金</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>股票</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -434,6 +454,7 @@
   <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.36328125" customWidth="1"/>
     <col min="7" max="7" width="13.81640625" customWidth="1"/>
@@ -471,12 +492,18 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Sheet2!$A$2:$A$5</xm:f>
+            <xm:f>Sheet2!$A$2:$A$6</xm:f>
           </x14:formula1>
           <xm:sqref>D2:D1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>Sheet2!$B$2:$B$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>A2:A1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -486,17 +513,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="1"/>
+      <c r="B1" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -509,25 +539,40 @@
       <c r="A2" t="s">
         <v>7</v>
       </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
     </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/AssetDeclarationCodeMaintenance001.xlsx
+++ b/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/AssetDeclarationCodeMaintenance001.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15840" windowHeight="1830"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>资产代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -26,43 +26,55 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>资产名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>申报开始日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>申报终止日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>申报价格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可转债信用申购</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配债</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配股</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新股申购</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>业务类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>资产类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>资产名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>申报开始日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>申报终止日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>申报价格</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可转债信用申购</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>配债</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>配股</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>新股申购</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>业务类型</t>
+    <t>债券</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>股票</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资产类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -145,7 +157,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -187,7 +199,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -222,7 +234,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -432,37 +444,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.81640625" customWidth="1"/>
+    <col min="6" max="6" width="14.375" customWidth="1"/>
+    <col min="7" max="7" width="13.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E1" t="s">
         <v>1</v>
       </c>
       <c r="F1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -471,13 +483,19 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet2!$A$2:$A$5</xm:f>
           </x14:formula1>
           <xm:sqref>D2:D1048576</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>Sheet2!$B$2:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>A2:A1048576</xm:sqref>
+        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -487,16 +505,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -505,24 +525,30 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
         <v>7</v>
       </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A5" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -534,7 +560,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
